--- a/output/full_scan/batch_seq8_2026-10-29.xlsx
+++ b/output/full_scan/batch_seq8_2026-10-29.xlsx
@@ -538,7 +538,7 @@
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>725.4368504664494</v>
+        <v>975.4368504664494</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>2090</v>
@@ -552,49 +552,49 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>57.85144471270152</v>
+        <v>57.85144471079356</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>16.17463252457983</v>
+        <v>16.17463248960625</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>2.852669188472293</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>31.3487512792119</v>
+        <v>31.34875128033312</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>6870</v>
+        <v>6902</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>騰雲</t>
+          <t>GOGOLOOK</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>699.5758721401835</v>
+        <v>872.4277553709848</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>397</v>
+        <v>160</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -605,16 +605,16 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>72.96678614479482</v>
+        <v>61.70656927615337</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>34.76606971746166</v>
+        <v>25.68524711026915</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>1.665743921372496</v>
+        <v>0.522829119441276</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L3" s="2" t="n">
         <v>0</v>
@@ -623,31 +623,31 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>7.76445747416702</v>
+        <v>1.899054621864033</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>6894</v>
+        <v>6870</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>衛司特</t>
+          <t>騰雲</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>665.4249049768206</v>
+        <v>839.5758721401835</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>405.5</v>
+        <v>397</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,13 +658,13 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>57.39613418406696</v>
+        <v>72.96678615351584</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>34.88145874606488</v>
+        <v>34.76606974279284</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.6679028781626956</v>
+        <v>1.665743921372496</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>0</v>
@@ -676,11 +676,11 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>2.061659391598461</v>
+        <v>7.764457473606324</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -697,7 +697,7 @@
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>647.6949182411278</v>
+        <v>787.6949182411278</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>249.5</v>
@@ -711,16 +711,16 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>73.55553519945803</v>
+        <v>73.55553518452088</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>43.65552376332021</v>
+        <v>43.65552381334808</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>1.427150135220881</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>0</v>
@@ -729,31 +729,31 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>4.678156708792146</v>
+        <v>4.678156709633157</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>6934</v>
+        <v>6894</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>心誠鎂</t>
+          <t>衛司特</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>625.5575659645892</v>
+        <v>720.4249049768205</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>84.5</v>
+        <v>405.5</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,13 +764,13 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>59.36963927178151</v>
+        <v>57.3961342127575</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>28.15845434987018</v>
+        <v>34.88145887753188</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.6557565964589244</v>
+        <v>0.6679028781626956</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>0</v>
@@ -782,31 +782,31 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.2005362288442516</v>
+        <v>2.061659391177983</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>6902</v>
+        <v>7704</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>GOGOLOOK</t>
+          <t>明遠精密</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>622.4277553709846</v>
+        <v>678.1003407060904</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>160</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,13 +817,13 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>61.7065693266478</v>
+        <v>83.07614894335018</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>25.68524705173327</v>
+        <v>30.04493231681417</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.522829119441276</v>
+        <v>3.410034070609035</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>0</v>
@@ -835,31 +835,31 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>1.899054621135138</v>
+        <v>2.105233145202963</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>6957</v>
+        <v>6873</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>裕慶-KY</t>
+          <t>泓德能源</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>608.7741823532465</v>
+        <v>627.0349444499847</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>444.5</v>
+        <v>50</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,16 +870,16 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>60.76781792430133</v>
+        <v>23.43533300423779</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>59.43038231622617</v>
+        <v>23.24212698651739</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.4047627803612377</v>
+        <v>6.92784161476913</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>-7.93792434732994</v>
+        <v>-1.762960014987879</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>7711</v>
+        <v>6952</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>永擎</t>
+          <t>大武山</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>588.0929528274968</v>
+        <v>619.9417116508589</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>561</v>
+        <v>40.05</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,16 +923,16 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>48.0301739349762</v>
+        <v>53.55945425334979</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>24.76043920295417</v>
+        <v>6.720494731437009</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.7441188108802993</v>
+        <v>0.571446464077153</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>-6.870710185393216</v>
+        <v>0.06126344279070517</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6877</v>
+        <v>7765</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>鏵友益</t>
+          <t>中華資安</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>581.53891007781</v>
+        <v>617.0386009495154</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>150</v>
+        <v>240</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,16 +976,16 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>56.49386378879238</v>
+        <v>56.71761933776581</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>28.31550680935244</v>
+        <v>25.90352746660676</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.5538910077809942</v>
+        <v>0.7046794467649913</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>-0.2786515596540573</v>
+        <v>0.486868416938163</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, above_ichimoku_cloud</t>
+          <t>rsi_strong, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>6873</v>
+        <v>7736</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>泓德能源</t>
+          <t>虎山</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>567.0349444499847</v>
+        <v>566.7296422466745</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>50</v>
+        <v>69.7</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,16 +1029,16 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>23.43533314822854</v>
+        <v>54.64283526299543</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>23.24212698809836</v>
+        <v>30.34868914678533</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>6.92784161476913</v>
+        <v>0.6105201114184944</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>-1.762960015128043</v>
+        <v>0.04037266856247373</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, avoid_chase, hist_turn_positive, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>6885</v>
+        <v>6934</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>全福生技</t>
+          <t>心誠鎂</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>556.3506274456408</v>
+        <v>565.5575659645892</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>28.4</v>
+        <v>84.5</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,16 +1082,16 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>45.35281906559309</v>
+        <v>59.36963917273719</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>32.88627906827949</v>
+        <v>28.15845460149654</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.5155885472561479</v>
+        <v>0.6557565964589244</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>-0.5462185146713823</v>
+        <v>0.200536229152616</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>6933</v>
+        <v>6971</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>AMAX-KY</t>
+          <t>惠民實業</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>541.5294494059815</v>
+        <v>564.9161034769324</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>371.5</v>
+        <v>25.45</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,13 +1135,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>50.10378466240667</v>
+        <v>65.40070399798294</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>42.07528835807061</v>
+        <v>17.47999132308639</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.7645258251824594</v>
+        <v>0.8541916955164888</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>-6.975273054368934</v>
+        <v>0.174365602265622</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, breakout_20d, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>6924</v>
+        <v>6957</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>榮惠-KY創</t>
+          <t>裕慶-KY</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>540.2566723239515</v>
+        <v>548.7741823532465</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>134</v>
+        <v>444.5</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,13 +1188,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>46.79819937483611</v>
+        <v>60.7678179332579</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>29.54208441927761</v>
+        <v>59.43038225475486</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.4288778250617318</v>
+        <v>0.4047627803612377</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>-1.51777820393539</v>
+        <v>-7.937924346909476</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>7704</v>
+        <v>7711</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>明遠精密</t>
+          <t>永擎</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>538.1003407060904</v>
+        <v>528.0929528274968</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>79.40000000000001</v>
+        <v>561</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,13 +1241,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>83.07614892444893</v>
+        <v>48.03017394951596</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>30.04493228541972</v>
+        <v>24.76043928095151</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>3.410034070609035</v>
+        <v>0.7441188108802993</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>2.105233145174929</v>
+        <v>-6.870710186794794</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>7765</v>
+        <v>7770</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>中華資安</t>
+          <t>君曜</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>537.0386009495154</v>
+        <v>524.3095748233608</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>240</v>
+        <v>41</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,13 +1294,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>56.71761998002723</v>
+        <v>56.22841457087493</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>25.90352728625728</v>
+        <v>20.05885901108318</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.7046794467649913</v>
+        <v>0.8897673576133897</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>0.4868684145552831</v>
+        <v>-0.01651454295064003</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>8021</v>
+        <v>6877</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>尖點</t>
+          <t>鏵友益</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>533.3021027090111</v>
+        <v>521.53891007781</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>428.5</v>
+        <v>150</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,16 +1347,16 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>36.86317103174235</v>
+        <v>56.49386380857685</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>22.98982517920794</v>
+        <v>28.31550688689932</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.9209263316293641</v>
+        <v>0.5538910077809942</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>-14.88310517764179</v>
+        <v>-0.2786515596540573</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>7736</v>
+        <v>6885</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>虎山</t>
+          <t>全福生技</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>486.7296422466745</v>
+        <v>496.3506274456408</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>69.7</v>
+        <v>28.4</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,13 +1400,13 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>54.64283510774879</v>
+        <v>45.3528191794547</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>30.3486891071915</v>
+        <v>32.88627897312861</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.6105201114184944</v>
+        <v>0.5155885472561479</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.04037266898296982</v>
+        <v>-0.5462185151199233</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>6971</v>
+        <v>6924</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>惠民實業</t>
+          <t>榮惠-KY創</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>484.9161034769325</v>
+        <v>480.2566723239516</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>25.45</v>
+        <v>134</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,13 +1453,13 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>65.40070433497699</v>
+        <v>46.79819932486392</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>17.47999128617139</v>
+        <v>29.54208439371718</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.8541916955164888</v>
+        <v>0.4288778250617318</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.1743656019011808</v>
+        <v>-1.517778203234529</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>7792</v>
+        <v>8021</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>安葆</t>
+          <t>尖點</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>475.2186144998078</v>
+        <v>473.3021027090112</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>324.5</v>
+        <v>428.5</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,49 +1506,49 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>39.07735192028756</v>
+        <v>36.86317105975215</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>28.26506302050993</v>
+        <v>22.98982513626064</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.4342902423007466</v>
+        <v>0.9209263316293641</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>-10.72129249123281</v>
+        <v>-14.88310517680079</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>6952</v>
+        <v>6933</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>大武山</t>
+          <t>AMAX-KY</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>454.9417116508588</v>
+        <v>471.5294494059816</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>40.05</v>
+        <v>371.5</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,13 +1559,13 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>53.5594542569084</v>
+        <v>50.10378472677404</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>6.720494679525423</v>
+        <v>42.07528836390009</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.571446464077153</v>
+        <v>0.7645258251824594</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>0.06126344276267881</v>
+        <v>-6.975273053808223</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>7770</v>
+        <v>6958</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>君曜</t>
+          <t>日盛台駿</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>444.3095748233606</v>
+        <v>444.7790192777839</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>41</v>
+        <v>16.85</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,16 +1612,16 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>56.22841422161245</v>
+        <v>45.8892551602871</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>20.05885911408068</v>
+        <v>20.09855068584067</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.8897673576133897</v>
+        <v>0.1599342380409859</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>-0.01651454194141705</v>
+        <v>0.005053390821938564</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, avoid_chase, hist_turn_positive, foreign_buy_3d, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>7738</v>
+        <v>6914</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>東聯互動</t>
+          <t>阜爾運通</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>437.1083121817282</v>
+        <v>438.8081424433836</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>162.5</v>
+        <v>115.5</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,16 +1665,16 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>50.59047512722137</v>
+        <v>33.76668538562767</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>29.69559947513564</v>
+        <v>39.21558158414383</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.5108312181728206</v>
+        <v>1.528273745606643</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.6211749341583388</v>
+        <v>0.2982889025060826</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>volume_break, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>6913</v>
+        <v>7805</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>鴻呈</t>
+          <t>威聯通</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>421.5247290093205</v>
+        <v>431.0322742952595</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>133.5</v>
+        <v>458</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,16 +1718,16 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>49.66521266360579</v>
+        <v>37.40002365359217</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>15.30155697310705</v>
+        <v>26.2162441108327</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.331473419639447</v>
+        <v>0.3273728961992262</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>-0.06340277724204862</v>
+        <v>0.4930006410810286</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, avoid_chase, hist_turn_positive, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>7751</v>
+        <v>7714</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>竑騰</t>
+          <t>創泓科技</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>419.2710739554173</v>
+        <v>428.8989204134781</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>1390</v>
+        <v>162</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,16 +1771,16 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>42.23529450001329</v>
+        <v>44.55765728090184</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>16.65346978073834</v>
+        <v>17.27174705794943</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.1738591530290277</v>
+        <v>0.2208854997043328</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>-25.30318701946082</v>
+        <v>-0.6630316845684253</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, avoid_chase, stronger_than_market, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>7810</v>
+        <v>8016</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>捷創科技</t>
+          <t>矽創</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>399.7282310277669</v>
+        <v>428.4465958037138</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>218.5</v>
+        <v>296</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,13 +1824,13 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>41.20921698287426</v>
+        <v>53.35863003311504</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>21.81313867067945</v>
+        <v>17.78844558471385</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.2049135912252414</v>
+        <v>0.663065898031468</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>-2.857735877966255</v>
+        <v>0.2151602571585802</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>6958</v>
+        <v>7760</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>日盛台駿</t>
+          <t>享溫馨</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>394.7790192777839</v>
+        <v>427.2165314001118</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>16.85</v>
+        <v>32.5</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,16 +1877,16 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>45.8892551602871</v>
+        <v>47.16997107428158</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>20.09855072368946</v>
+        <v>42.29294357883222</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.1599342380409859</v>
+        <v>1.025517522052133</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0.005053390821938564</v>
+        <v>0.01085745038305483</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, kd_golden_cross</t>
+          <t>avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>7812</v>
+        <v>8028</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>稜研科技*-創</t>
+          <t>昇陽半導體</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>391.1551193427748</v>
+        <v>426.9366925054024</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>61.9</v>
+        <v>255.5</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,16 +1930,16 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>34.49398113242492</v>
+        <v>46.67485826603281</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>26.25318501777627</v>
+        <v>18.56823844942508</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.8534770344071327</v>
+        <v>0.4089276373912009</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>0.08081880025305255</v>
+        <v>-2.757575374831646</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, foreign_buy_3d, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>6919</v>
+        <v>7786</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>康霈*</t>
+          <t>東方風能</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>389.449991206362</v>
+        <v>423.4170581949144</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>65.40000000000001</v>
+        <v>123</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,13 +1983,13 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>22.56646455351078</v>
+        <v>54.93072120192739</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>40.06065257734301</v>
+        <v>24.0477581545575</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>2.41550047892302</v>
+        <v>1.0799778903731</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>-0.6200173681587171</v>
+        <v>0.9376112536274864</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>7828</v>
+        <v>7792</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>創新服務</t>
+          <t>安葆</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>384.7063142626233</v>
+        <v>415.2186144998078</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>1340</v>
+        <v>324.5</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,13 +2036,13 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>26.77228429556828</v>
+        <v>39.07735187497912</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>26.87195453398424</v>
+        <v>28.26506306459176</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.5398755747404732</v>
+        <v>0.4342902423007466</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>-39.08101506156518</v>
+        <v>-10.72129248969089</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>6937</v>
+        <v>6835</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>天虹</t>
+          <t>圓裕</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>380.0324454383901</v>
+        <v>410.7927242439625</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>260</v>
+        <v>32</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,16 +2089,16 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>35.33553141769347</v>
+        <v>52.60964126997683</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>23.86219136636437</v>
+        <v>19.03129017029531</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.3574303760824378</v>
+        <v>0.8153063030686628</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>-3.144568880392449</v>
+        <v>-0.002288568208921454</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>7805</v>
+        <v>7812</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>威聯通</t>
+          <t>稜研科技*-創</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>376.0322742952595</v>
+        <v>406.1551193427748</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>458</v>
+        <v>61.9</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,16 +2142,16 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>37.40002398201193</v>
+        <v>34.49398111511246</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>26.21624353364824</v>
+        <v>26.2531849745168</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.3273728961992262</v>
+        <v>0.8534770344071327</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.4930006321102098</v>
+        <v>0.0808188003371586</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
+          <t>avoid_chase, adx_trending, kd_golden_cross, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>7714</v>
+        <v>6988</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>創泓科技</t>
+          <t>威力暘-創</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>373.8989204134781</v>
+        <v>399.0790823691262</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>162</v>
+        <v>12.1</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,16 +2195,16 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>44.55765724101666</v>
+        <v>47.84638035644948</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>17.27174697789546</v>
+        <v>16.15804281831257</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.2208854997043328</v>
+        <v>0.06215873181298782</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>-0.6630316879324707</v>
+        <v>-0.06277192826573334</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>7795</v>
+        <v>6965</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>長廣</t>
+          <t>中傑-KY</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>373.8597102428855</v>
+        <v>398.4630622493756</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>409</v>
+        <v>65</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,16 +2248,16 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>33.19254618966906</v>
+        <v>42.88808201608138</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>25.80399615811302</v>
+        <v>32.56434638440127</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.4056216612420525</v>
+        <v>0.1535590598325667</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>-10.57250391772769</v>
+        <v>0.3399065072393492</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>7772</v>
+        <v>7769</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>耀穎</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>373.1829643248433</v>
+        <v>394.8571375994338</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>101.5</v>
+        <v>5190</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,49 +2301,49 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>33.48872253660321</v>
+        <v>41.4776165441214</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>30.63161642226449</v>
+        <v>14.39350704524773</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.517118546428461</v>
+        <v>0.8930399544401956</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L35" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M35" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>-5.621777630610763</v>
+        <v>-20.99804989199711</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, invest_trust_buy_2d, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>7786</v>
+        <v>7712</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>東方風能</t>
+          <t>博盛半導體</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>368.4170581949138</v>
+        <v>392.817500181008</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>123</v>
+        <v>146.5</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,13 +2354,13 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>54.9307212663288</v>
+        <v>42.32258412936425</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>24.04775816554247</v>
+        <v>22.96825917492588</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>1.0799778903731</v>
+        <v>0.665032713537268</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>0.9376112530668058</v>
+        <v>-2.159146634700346</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>7799</v>
+        <v>6887</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>禾榮科</t>
+          <t>寶綠特-KY</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>368.2952215993272</v>
+        <v>381.7008466610358</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>437.5</v>
+        <v>35.45</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,16 +2407,16 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>43.73768851061873</v>
+        <v>45.42556699184876</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>27.34369851495423</v>
+        <v>20.72767477586299</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.2066921574019476</v>
+        <v>0.9449769338418073</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>-9.487518507919974</v>
+        <v>-0.08395793794580264</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>6861</v>
+        <v>7738</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>睿生光電</t>
+          <t>東聯互動</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>366.1943013690973</v>
+        <v>377.1083121817282</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>232.5</v>
+        <v>162.5</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,16 +2460,16 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>44.34486571905482</v>
+        <v>50.5904751091919</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>21.46261090390256</v>
+        <v>29.69559947083652</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.3025135334342778</v>
+        <v>0.5108312181728206</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>-5.421696442191799</v>
+        <v>0.62117493387802</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>7556</v>
+        <v>6944</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>意德士</t>
+          <t>兆聯實業</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>365.4393919964475</v>
+        <v>374.2583183713536</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>267</v>
+        <v>780</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,16 +2513,16 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>46.0955774080279</v>
+        <v>50.96886979771597</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>22.9967772323709</v>
+        <v>20.39475996903207</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.333339080249215</v>
+        <v>0.3548815068310889</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>-3.04684198480066</v>
+        <v>-6.103040496906576</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>avoid_chase, liquidity_ok, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>7610</v>
+        <v>6913</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>聯友金屬-創</t>
+          <t>鴻呈</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>365.39350609219</v>
+        <v>361.5247290093205</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>1330</v>
+        <v>133.5</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,16 +2566,16 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>33.61148041035675</v>
+        <v>49.66521254418775</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>23.35849309908234</v>
+        <v>15.30155703837139</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.433635760750622</v>
+        <v>0.331473419639447</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>-23.23255510160922</v>
+        <v>-0.06340277626088725</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>8032</v>
+        <v>7751</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>光菱</t>
+          <t>竑騰</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>364.4815898034643</v>
+        <v>359.2710739554173</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>34.4</v>
+        <v>1390</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,16 +2619,16 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>42.41058858829475</v>
+        <v>42.23529456499314</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>23.76958564769356</v>
+        <v>16.65346978073834</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>1.579273375509441</v>
+        <v>0.1738591530290277</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>-0.09613809974018328</v>
+        <v>-25.30318701876</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>6838</v>
+        <v>7547</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>台新藥</t>
+          <t>碩網</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>356.2265632202241</v>
+        <v>356.6450843320747</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>24.8</v>
+        <v>58.4</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,16 +2672,16 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>48.6150775382278</v>
+        <v>52.36087310380571</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>24.96741216236384</v>
+        <v>19.15018458679935</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.353729144888188</v>
+        <v>0.4254760429530021</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>-0.1216835934080968</v>
+        <v>-0.5321424194785638</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>avoid_chase, stronger_than_market, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>6988</v>
+        <v>6947</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>威力暘-創</t>
+          <t>台鎔科技</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>349.0790823691262</v>
+        <v>354.8806306279444</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>12.1</v>
+        <v>66.7</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,16 +2725,16 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>47.84638041172325</v>
+        <v>39.88403336414923</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>16.15804283328517</v>
+        <v>12.98088444830976</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.06215873181298782</v>
+        <v>2.453260687536317</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>-0.06277192826573334</v>
+        <v>0.03271910118438592</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, avoid_chase, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>6965</v>
+        <v>6928</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>中傑-KY</t>
+          <t>攸泰科技</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>348.4630622493756</v>
+        <v>345.6508050008418</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>65</v>
+        <v>46.2</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,16 +2778,16 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>42.88808221283042</v>
+        <v>50.46115450342561</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>32.56434609127635</v>
+        <v>11.67781010276903</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.1535590598325667</v>
+        <v>0.5794980472945906</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.339906506874895</v>
+        <v>0.2439373120749398</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>8016</v>
+        <v>6921</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>矽創</t>
+          <t>嘉雨思-創</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>348.4465958037119</v>
+        <v>345.1348848325586</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>296</v>
+        <v>65.5</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,16 +2831,16 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>53.35863003311504</v>
+        <v>53.07549042563109</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>17.78844565465014</v>
+        <v>14.80872838701056</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.663065898031468</v>
+        <v>0.09372532387957233</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.2151602567381063</v>
+        <v>-0.7138303327008231</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>avoid_chase, foreign_buy_3d, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>6997</v>
+        <v>7810</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>博弘</t>
+          <t>捷創科技</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>340.6819953788005</v>
+        <v>339.7282310277669</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>0</v>
+        <v>218.5</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>37.46759520780725</v>
+        <v>41.20921688746311</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>10.25015321275433</v>
+        <v>21.81313869868515</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0</v>
+        <v>0.2049135912252414</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>-2.513502468774254</v>
+        <v>-2.85773587754576</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>7712</v>
+        <v>6919</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>博盛半導體</t>
+          <t>康霈*</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>337.8175001810079</v>
+        <v>339.449991206362</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>146.5</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,16 +2937,16 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>42.32258411039842</v>
+        <v>22.5664640048727</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>22.96825909993309</v>
+        <v>40.06065269129728</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.665032713537268</v>
+        <v>2.41550047892302</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>-2.159146634840505</v>
+        <v>-0.620017365074975</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>volume_break, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>6890</v>
+        <v>7855</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>來億-KY</t>
+          <t>和運租車</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>332.2588276938227</v>
+        <v>339.4200324843978</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>142.5</v>
+        <v>41.35</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,16 +2990,16 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>38.65417214579094</v>
+        <v>27.92847803861237</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>9.744126710758245</v>
+        <v>46.77925130742077</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>1.015787757428569</v>
+        <v>1.069333572633527</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-0.03575265956080642</v>
+        <v>0.4083900998361689</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>8011</v>
+        <v>7856</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>台通</t>
+          <t>漢測</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>323.6322954200081</v>
+        <v>339.1871788052068</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>16.1</v>
+        <v>3505</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,49 +3043,49 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>46.28138667340286</v>
+        <v>38.98517066018146</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>24.59563975922021</v>
+        <v>19.54105929266792</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.2354344711436698</v>
+        <v>0.576369899335513</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L49" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M49" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-0.04675046182763626</v>
+        <v>-18.58212413177728</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>6840</v>
+        <v>6949</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>東研信超</t>
+          <t>沛爾生醫-創</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>319.5788176440327</v>
+        <v>334.5114956274045</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>76</v>
+        <v>40.8</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,13 +3096,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>26.05165481877833</v>
+        <v>27.00077176564452</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>34.02683800935209</v>
+        <v>46.64776603051037</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.2590217851107824</v>
+        <v>0.6162530069683476</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>1</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>-1.642016126021518</v>
+        <v>26.15520911588878</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>liquidity_ok, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>7717</v>
+        <v>6909</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>萊德光電-KY</t>
+          <t>創控</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>314.0966464788941</v>
+        <v>326.1725118078696</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>423</v>
+        <v>46.5</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,16 +3149,16 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>36.87482241307269</v>
+        <v>52.63947557763132</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>19.38111485876965</v>
+        <v>35.74197693068535</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.40532598184899</v>
+        <v>0.4880877111177088</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>-14.40974298891094</v>
+        <v>-0.04261423471543324</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>6855</v>
+        <v>7828</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>數泓科</t>
+          <t>創新服務</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>306.0430001326762</v>
+        <v>324.7063142626232</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>108.5</v>
+        <v>1340</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>51.61988970212934</v>
+        <v>26.77228422225018</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>6.737077341303147</v>
+        <v>26.87195465627683</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.2727911755163837</v>
+        <v>0.5398755747404732</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0.0739616151538689</v>
+        <v>-39.08101505077234</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>7744</v>
+        <v>6937</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>崴寶</t>
+          <t>天虹</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>304.6810967099348</v>
+        <v>320.0324454383901</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>457</v>
+        <v>260</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>37.04400313467088</v>
+        <v>35.33553156957106</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>31.89121776620906</v>
+        <v>23.86219136689077</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.996969817016097</v>
+        <v>0.3574303760824378</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>-5.657627065260517</v>
+        <v>-3.14456887660791</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>6918</v>
+        <v>7795</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>愛派司</t>
+          <t>長廣</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>302.892032835222</v>
+        <v>313.8597102428854</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>74.09999999999999</v>
+        <v>409</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>46.9042702525344</v>
+        <v>33.1925461741145</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>23.92096837811792</v>
+        <v>25.80399613260803</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.1424474297973897</v>
+        <v>0.4056216612420525</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>-0.0603090383274559</v>
+        <v>-10.57250391716703</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>7547</v>
+        <v>7772</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>碩網</t>
+          <t>耀穎</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>301.6450843320748</v>
+        <v>313.1829643248432</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>58.4</v>
+        <v>101.5</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,16 +3361,16 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>52.36087303600079</v>
+        <v>33.48872257769736</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>19.1501846627302</v>
+        <v>30.63161644912725</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.4254760429530021</v>
+        <v>0.517118546428461</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>-0.532142419338391</v>
+        <v>-5.621777630863084</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>6953</v>
+        <v>6962</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>家碩</t>
+          <t>奕力-KY</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>300.5478775594453</v>
+        <v>311.8173272204301</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>229.5</v>
+        <v>31.05</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,13 +3414,13 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>41.453651253874</v>
+        <v>45.83063851084307</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>14.28240291543264</v>
+        <v>12.66783364353465</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.08669347262410282</v>
+        <v>0.6735783251066356</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-2.233464903704697</v>
+        <v>-0.1097910014553987</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>6947</v>
+        <v>7799</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>台鎔科技</t>
+          <t>禾榮科</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>299.8806306279444</v>
+        <v>308.2952215993272</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>66.7</v>
+        <v>437.5</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,13 +3467,13 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>39.88403250410006</v>
+        <v>43.73768856342082</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>12.98088442659984</v>
+        <v>27.34369851495423</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>2.453260687536317</v>
+        <v>0.2066921574019476</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>0.03271910098814002</v>
+        <v>-9.487518505116537</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>7631</v>
+        <v>6861</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>聚賢研發-創</t>
+          <t>睿生光電</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>299.8094058507727</v>
+        <v>306.1943013690973</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>126</v>
+        <v>232.5</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,13 +3520,13 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>31.5005838382688</v>
+        <v>44.34486572749807</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>21.18089567819282</v>
+        <v>21.46261091736609</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.3379446600514369</v>
+        <v>0.3025135334342778</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-1.17690358648678</v>
+        <v>-5.421696442219832</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>6907</v>
+        <v>7556</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>雅特力-KY</t>
+          <t>意德士</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>298.5536972634919</v>
+        <v>305.4393919964484</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>145.5</v>
+        <v>267</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,13 +3573,13 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>30.75883020899487</v>
+        <v>46.09557748939479</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>18.75466011276038</v>
+        <v>22.9967772323709</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.7408422279053052</v>
+        <v>0.333339080249215</v>
       </c>
       <c r="K59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>-3.449239839614332</v>
+        <v>-3.046841985081043</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>6928</v>
+        <v>7610</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>攸泰科技</t>
+          <t>聯友金屬-創</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>295.6508050008449</v>
+        <v>305.3935060921901</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>46.2</v>
+        <v>1330</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>50.46115443686489</v>
+        <v>33.61148041204108</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>11.67780998413165</v>
+        <v>23.35849317760151</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.5794980472945906</v>
+        <v>0.433635760750622</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>0.2439373124954513</v>
+        <v>-23.2325551023101</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>7855</v>
+        <v>8032</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>和運租車</t>
+          <t>光菱</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>289.4200324843978</v>
+        <v>304.4815898034647</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>41.35</v>
+        <v>34.4</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>27.92847803861237</v>
+        <v>42.41058855270326</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>46.77925130742077</v>
+        <v>23.76958559176763</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>1.069333572633527</v>
+        <v>1.579273375509441</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>0.4083900998361689</v>
+        <v>-0.09613809971214682</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>volume_break, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>7710</v>
+        <v>6838</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>東擎科技</t>
+          <t>台新藥</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>288.6296104286961</v>
+        <v>296.2265632202241</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>134.5</v>
+        <v>24.8</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>23.1551121501637</v>
+        <v>48.61507784811236</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>27.66495344664087</v>
+        <v>24.96741219341842</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>2.762961042869613</v>
+        <v>0.353729144888188</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-5.931081334211752</v>
+        <v>-0.121683593646387</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>avoid_chase, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>7788</v>
+        <v>6910</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>松川精密</t>
+          <t>德鴻</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>282.961482002799</v>
+        <v>293.6397534884802</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>259</v>
+        <v>25.2</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>38.68553322798189</v>
+        <v>47.99269426788734</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>14.94016262662976</v>
+        <v>23.28661474657427</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.6104122554068246</v>
+        <v>0.403711123333427</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>-5.222792230183487</v>
+        <v>-0.04072424770816453</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>avoid_chase, adx_trending, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>7822</v>
+        <v>7821</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>倍利科</t>
+          <t>神數</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>281.6855531521097</v>
+        <v>284.02243897915</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>766</v>
+        <v>34.85</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,16 +3838,16 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>31.22518368850409</v>
+        <v>36.07649690127904</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>22.43672775225302</v>
+        <v>30.26890951649634</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.372765936791252</v>
+        <v>0.992633744805676</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-13.86883736828238</v>
+        <v>0.04819316756645442</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>7747</v>
+        <v>6997</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>昕奇雲端</t>
+          <t>博弘</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>278.1150362443595</v>
+        <v>280.6819953788006</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>51.22380982750891</v>
+        <v>37.46759521099278</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>5.061726583820147</v>
+        <v>10.25015328169685</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.189276688894531</v>
+        <v>0</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>0.4381896744459723</v>
+        <v>-2.513502469194766</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
+          <t>avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>6944</v>
+        <v>7820</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>兆聯實業</t>
+          <t>立盈</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>274.2583183713535</v>
+        <v>277.5374752761069</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>780</v>
+        <v>104</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>50.96886979771597</v>
+        <v>51.98524093439853</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>20.39475998663097</v>
+        <v>11.41321183407073</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.3548815068310889</v>
+        <v>0.1268444531594686</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>-6.103040498588699</v>
+        <v>-0.1344494824302309</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>stronger_than_market, williams_r_recovery, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>6914</v>
+        <v>6890</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>阜爾運通</t>
+          <t>來億-KY</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>273.8081424433837</v>
+        <v>272.258827693823</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>115.5</v>
+        <v>142.5</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>33.76668525003495</v>
+        <v>38.65417237701011</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>39.21558155282265</v>
+        <v>9.744126702013698</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>1.528273745606643</v>
+        <v>1.015787757428569</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>0.2982889030667479</v>
+        <v>-0.03575266096250385</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>6936</v>
+        <v>8011</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>永鴻生技</t>
+          <t>台通</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>272.714594207913</v>
+        <v>263.6322954199997</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>32.2</v>
+        <v>16.1</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,16 +4050,16 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>50.45607575169637</v>
+        <v>46.28138679562245</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>16.12237089597169</v>
+        <v>24.59563974625963</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>1.144495060654143</v>
+        <v>0.2354344711436698</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-0.007602029386916842</v>
+        <v>-0.04675046186968709</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>6895</v>
+        <v>6840</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>宏碩系統</t>
+          <t>東研信超</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>270.1192852496266</v>
+        <v>259.5788176440327</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>134</v>
+        <v>76</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,13 +4103,13 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>35.08053419355772</v>
+        <v>26.05165462533783</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>26.12828957883675</v>
+        <v>34.02683810334631</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>1.886848868148047</v>
+        <v>0.2590217851107824</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>1</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>-2.396715919289531</v>
+        <v>-1.642016125124441</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>7825</v>
+        <v>7791</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>和亞智慧</t>
+          <t>皇家可口</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>267.7725400957176</v>
+        <v>257.9752487244092</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>60.8</v>
+        <v>49.3</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,16 +4156,16 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>30.41360784285229</v>
+        <v>29.06469691406751</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>21.53047305250189</v>
+        <v>46.11997198128957</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.464758417260794</v>
+        <v>0.3454542488458213</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>-0.8068130257076147</v>
+        <v>-0.1384727674236919</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>6901</v>
+        <v>7717</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>鑽石投資</t>
+          <t>萊德光電-KY</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>267.0033482933867</v>
+        <v>254.0966464788941</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>16.45</v>
+        <v>423</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,16 +4209,16 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>46.36330868609826</v>
+        <v>36.87482241307269</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>23.10713464558493</v>
+        <v>19.38111485876965</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.2499540580815544</v>
+        <v>0.40532598184899</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-0.164547785694182</v>
+        <v>-14.40974298891094</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>avoid_chase, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>6909</v>
+        <v>7689</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>創控</t>
+          <t>大鵬科CLMX</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>266.1725118078853</v>
+        <v>250.5500365346578</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>46.5</v>
+        <v>129.5</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,16 +4262,16 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>52.63947546805779</v>
+        <v>17.77489799734886</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>35.74197675060076</v>
+        <v>39.00789613401232</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.4880877111177088</v>
+        <v>2.75500365346578</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-0.04261423463133163</v>
+        <v>-1.236004990643405</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>volume_break, avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>7769</v>
+        <v>7744</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>崴寶</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>264.8571375994317</v>
+        <v>244.6810967099347</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>5190</v>
+        <v>457</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>41.47761654800509</v>
+        <v>37.04400317391094</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>14.39350697986386</v>
+        <v>31.8912179950774</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.8930399544401956</v>
+        <v>0.996969817016097</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-20.99804990601501</v>
+        <v>-5.657627068204075</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>7760</v>
+        <v>7803</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>享溫馨</t>
+          <t>雲象科技-創</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>262.2165314001116</v>
+        <v>243.2642916771634</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>32.5</v>
+        <v>14.05</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,16 +4368,16 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>47.16997109100046</v>
+        <v>21.42492552088321</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>42.29294357883221</v>
+        <v>27.42058379778153</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>1.025517522052133</v>
+        <v>1.226429167716345</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>0.01085745038305483</v>
+        <v>-0.2929836697082588</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>8028</v>
+        <v>6918</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>昇陽半導體</t>
+          <t>愛派司</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>261.9366925054024</v>
+        <v>242.892032835222</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>255.5</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>46.67485823593878</v>
+        <v>46.90427014611736</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>18.56823846788659</v>
+        <v>23.92096832225257</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.4089276373912009</v>
+        <v>0.1424474297973897</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-2.757575375812843</v>
+        <v>-0.06030903813119978</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>7842</v>
+        <v>6922</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>天能綠電</t>
+          <t>宸曜</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>259.4796474710051</v>
+        <v>241.9264768993948</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>94.3</v>
+        <v>194.5</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>51.42702949128114</v>
+        <v>45.76150227987728</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>11.83785651048682</v>
+        <v>17.33952797124684</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.3118660489902201</v>
+        <v>0.2786182649751484</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>2.067619380213408</v>
+        <v>-1.146506082749835</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>7827</v>
+        <v>6953</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>漢康-KY創</t>
+          <t>家碩</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>259.2651956551986</v>
+        <v>240.5478775594453</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>138</v>
+        <v>229.5</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>24.56130954472761</v>
+        <v>41.45365145403922</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>22.28106326334372</v>
+        <v>14.2824029443273</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.3265195655198571</v>
+        <v>0.08669347262410282</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>-3.162222256896908</v>
+        <v>-2.233464902723509</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>7856</v>
+        <v>7631</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>漢測</t>
+          <t>聚賢研發-創</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>259.1871788052068</v>
+        <v>239.8094058507726</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>3505</v>
+        <v>126</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,49 +4580,49 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>38.98517066018146</v>
+        <v>31.50058362304766</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>19.54105929266792</v>
+        <v>21.1808957133834</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.576369899335513</v>
+        <v>0.3379446600514369</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L78" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M78" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-18.58212413177728</v>
+        <v>-1.176903585225247</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>6859</v>
+        <v>6907</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>伯特光</t>
+          <t>雅特力-KY</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>258.0349050756989</v>
+        <v>238.5536972634919</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>110.5</v>
+        <v>145.5</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>35.79807238775788</v>
+        <v>30.75883020899487</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>21.11148398317671</v>
+        <v>18.75466011276038</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.7780282896477019</v>
+        <v>0.7408422279053052</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>-1.047340866865323</v>
+        <v>-3.449239839614332</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>7402</v>
+        <v>7710</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>邑錡</t>
+          <t>東擎科技</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>257.3532994829095</v>
+        <v>228.6296104286961</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>91.2</v>
+        <v>134.5</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,16 +4686,16 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>32.52666368319088</v>
+        <v>23.1551121501637</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>19.55372326352042</v>
+        <v>27.66495344664087</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.7973425773479959</v>
+        <v>2.762961042869613</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>-0.3033660314050621</v>
+        <v>-5.931081334211752</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d</t>
+          <t>volume_break, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>6865</v>
+        <v>6901</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>偉康科技</t>
+          <t>鑽石投資</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>256.8321105188638</v>
+        <v>227.0033482933867</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>26.55</v>
+        <v>16.45</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,16 +4739,16 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>50.56782780443407</v>
+        <v>46.36330869774398</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>10.66349881947254</v>
+        <v>23.10713464102179</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>1.187310186325207</v>
+        <v>0.2499540580815544</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>0.2543147412945711</v>
+        <v>-0.1645477856240942</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>6962</v>
+        <v>6869</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>奕力-KY</t>
+          <t>雲豹能源</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>256.8173272204301</v>
+        <v>226.979326214545</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>31.05</v>
+        <v>67.3</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,16 +4792,16 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>45.83063851792957</v>
+        <v>44.76671036262927</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>12.66783364441574</v>
+        <v>17.17918502280378</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.6735783251066356</v>
+        <v>0.4395255278669921</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>-0.1097910017357386</v>
+        <v>-0.5168553828573514</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>avoid_chase, foreign_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>7818</v>
+        <v>7788</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>溢泰實業</t>
+          <t>松川精密</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>256.359545401331</v>
+        <v>222.961482002799</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>58</v>
+        <v>259</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,13 +4845,13 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>26.29119182356749</v>
+        <v>38.68553316616795</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>26.2582180750537</v>
+        <v>14.94016255418565</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.5359545401331016</v>
+        <v>0.6104122554068246</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-0.1499775043404841</v>
+        <v>-5.222792228361231</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>7703</v>
+        <v>7822</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>銳澤</t>
+          <t>倍利科</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>249.2086098055247</v>
+        <v>221.6855531521099</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>176</v>
+        <v>766</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,13 +4898,13 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>32.64066075219269</v>
+        <v>31.22518373241194</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>31.25724861969701</v>
+        <v>22.43672777860415</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.270337659891638</v>
+        <v>0.372765936791252</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>-2.222551528469166</v>
+        <v>-13.86883737220708</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>6835</v>
+        <v>7747</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>圓裕</t>
+          <t>昕奇雲端</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>245.7927242439624</v>
+        <v>218.1150362443595</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>32</v>
+        <v>109</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,13 +4951,13 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>52.60964128197672</v>
+        <v>51.22380981007415</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>19.03129021772715</v>
+        <v>5.061726703799405</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.8153063030686628</v>
+        <v>0.189276688894531</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-0.00228856816687148</v>
+        <v>0.4381896751468228</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>6996</v>
+        <v>6936</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>力領科技</t>
+          <t>永鴻生技</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>245.1228643108543</v>
+        <v>212.7145942079128</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>160.5</v>
+        <v>32.2</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,16 +5004,16 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>36.55095722789444</v>
+        <v>50.45607577611511</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>31.31105457442456</v>
+        <v>16.1223709494368</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>1.012554004633706</v>
+        <v>1.144495060654143</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-0.1261366403057074</v>
+        <v>-0.007602029400933984</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>7749</v>
+        <v>6895</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>意騰-KY</t>
+          <t>宏碩系統</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>242.5592669045276</v>
+        <v>210.1192852496265</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>316</v>
+        <v>134</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,16 +5057,16 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>31.59629625597486</v>
+        <v>35.08053346840026</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>28.94717547621031</v>
+        <v>26.12829006330193</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.3105370405580684</v>
+        <v>1.886848868148047</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-4.60680036977852</v>
+        <v>-2.396715910879334</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>volume_break, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>6916</v>
+        <v>7825</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>華凌</t>
+          <t>和亞智慧</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>241.0209953900919</v>
+        <v>207.7725400957176</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>18.25</v>
+        <v>60.8</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,13 +5110,13 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>42.57458353033675</v>
+        <v>30.41360799159362</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>22.50309412058027</v>
+        <v>21.53047310419967</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.7346070629652719</v>
+        <v>0.464758417260794</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-0.1007315975688407</v>
+        <v>-0.8068130263434243</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>6910</v>
+        <v>7842</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>德鴻</t>
+          <t>天能綠電</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>238.6397534884833</v>
+        <v>199.4796474710051</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>25.2</v>
+        <v>94.3</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,13 +5163,13 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>47.99269368337398</v>
+        <v>51.42702947607271</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>23.2866147318849</v>
+        <v>11.83785652348515</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.403711123333427</v>
+        <v>0.3118660489902201</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-0.0407242470073159</v>
+        <v>2.067619380073235</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>8024</v>
+        <v>7827</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>佑華</t>
+          <t>漢康-KY創</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>235.0961078031716</v>
+        <v>199.2651956551986</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>11.85</v>
+        <v>138</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>36.54223512539714</v>
+        <v>24.56130961373097</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>24.22777464357411</v>
+        <v>22.28106326257648</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.272039587093634</v>
+        <v>0.3265195655198571</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>-0.02565662044440115</v>
+        <v>-3.162222256616572</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>7821</v>
+        <v>6859</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>神數</t>
+          <t>伯特光</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>234.02243897915</v>
+        <v>198.0349050756986</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>34.85</v>
+        <v>110.5</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,13 +5269,13 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>36.07649677615606</v>
+        <v>35.79807238775788</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>30.26890953462649</v>
+        <v>21.1114840132771</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.992633744805676</v>
+        <v>0.7780282896477019</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>0.0481931674262811</v>
+        <v>-1.047340867005492</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>6983</v>
+        <v>7402</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>華洋精機</t>
+          <t>邑錡</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>233.3733815083183</v>
+        <v>197.3532994829095</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>292.5</v>
+        <v>91.2</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,16 +5322,16 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>26.04673424715126</v>
+        <v>32.52666375776958</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>23.62192871939835</v>
+        <v>19.55372319104268</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.5278550201289791</v>
+        <v>0.7973425773479959</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-8.837363514085123</v>
+        <v>-0.3033660276204682</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>6862</v>
+        <v>6865</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>三集瑞-KY</t>
+          <t>偉康科技</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>224.6415993592047</v>
+        <v>196.8321105188639</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>133</v>
+        <v>26.55</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,13 +5375,13 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>42.88363023022202</v>
+        <v>50.56782783448061</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>15.71230681616658</v>
+        <v>10.66349884091334</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.4773898141417786</v>
+        <v>1.187310186325207</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>-1.115071960393169</v>
+        <v>0.2543147409861997</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>6949</v>
+        <v>7818</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>沛爾生醫-創</t>
+          <t>溢泰實業</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>224.5114956274045</v>
+        <v>196.359545401331</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>40.8</v>
+        <v>58</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,13 +5428,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>27.00077176564452</v>
+        <v>26.29119062097904</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>46.64776581635903</v>
+        <v>26.25821883136213</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.6162530069683476</v>
+        <v>0.5359545401331016</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>26.15520909619026</v>
+        <v>-0.1499775033592904</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok, adx_trending</t>
+          <t>avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>6863</v>
+        <v>6931</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>永道-KY</t>
+          <t>青松健康</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>223.103764062786</v>
+        <v>195.7361437513163</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>95</v>
+        <v>37.5</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,16 +5481,16 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>40.03632440196039</v>
+        <v>32.95435903342121</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>17.99811719544479</v>
+        <v>13.60208796747497</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.4265669980208708</v>
+        <v>0.975460795551073</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-0.1251140880516433</v>
+        <v>-0.002195292316374053</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>7839</v>
+        <v>7703</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>達人網</t>
+          <t>銳澤</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>222.4861976893032</v>
+        <v>189.2086098055247</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>43</v>
+        <v>176</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>40.28133596675257</v>
+        <v>32.64066085563435</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>26.92297057369458</v>
+        <v>31.257248619697</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.5297056179519567</v>
+        <v>0.270337659891638</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-0.07208306601116841</v>
+        <v>-2.222551528329009</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>6903</v>
+        <v>6855</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>巨漢</t>
+          <t>數泓科</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>219.1730641776667</v>
+        <v>186.0430001326761</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>299</v>
+        <v>108.5</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>41.44320708868695</v>
+        <v>51.61988922581313</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>19.50638013339358</v>
+        <v>6.737076682377126</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.5000207673776802</v>
+        <v>0.2727911755163837</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-3.29962253580461</v>
+        <v>0.07396165019633116</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>7734</v>
+        <v>6996</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>印能科技</t>
+          <t>力領科技</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>218.2313890944335</v>
+        <v>185.1228643108578</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>2235</v>
+        <v>160.5</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,16 +5640,16 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>36.95745559182859</v>
+        <v>36.55095737455432</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>18.61494751539336</v>
+        <v>31.31105443940446</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.545756833530492</v>
+        <v>1.012554004633706</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-29.92112222099807</v>
+        <v>-0.1261366401655386</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>6887</v>
+        <v>7749</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>寶綠特-KY</t>
+          <t>意騰-KY</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>216.7008466610384</v>
+        <v>182.5592669045276</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>35.45</v>
+        <v>316</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,13 +5693,13 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>45.4255669585564</v>
+        <v>31.59629595466374</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>20.72767473689917</v>
+        <v>28.94717558017343</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.9449769338418073</v>
+        <v>0.3105370405580684</v>
       </c>
       <c r="K99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-0.0839579379177674</v>
+        <v>-4.606800364452113</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>6923</v>
+        <v>6916</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>中台</t>
+          <t>華凌</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>215.1312076902414</v>
+        <v>181.0209953900919</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>71.5</v>
+        <v>18.25</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,13 +5746,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>31.15340694426921</v>
+        <v>42.57458346771388</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>10.79851076881903</v>
+        <v>22.50309412058027</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.3792444600082324</v>
+        <v>0.7346070629652719</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-0.1205463479241335</v>
+        <v>-0.1007315975267878</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>6955</v>
+        <v>6906</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>邦睿生技-創</t>
+          <t>現觀科</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>210.8280531804478</v>
+        <v>179.4518332609744</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>90</v>
+        <v>75.7</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,16 +5799,16 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>46.23918565618576</v>
+        <v>35.95912608454373</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>8.564714473230923</v>
+        <v>19.24489216037317</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>1.282805318044778</v>
+        <v>0.9167521946204261</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>0.03683247819498692</v>
+        <v>-0.5334500727236198</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>7791</v>
+        <v>8024</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>皇家可口</t>
+          <t>佑華</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>207.9752487244093</v>
+        <v>175.0961078031716</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>49.3</v>
+        <v>11.85</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,13 +5852,13 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>29.06469691406751</v>
+        <v>36.54223514194562</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>46.11997198128957</v>
+        <v>24.22777457611887</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.3454542488458213</v>
+        <v>0.272039587093634</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-0.1384727672835182</v>
+        <v>-0.0256566204584171</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>7715</v>
+        <v>6983</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>裕山</t>
+          <t>華洋精機</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>201.9905539996138</v>
+        <v>173.3733815083185</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>25.1</v>
+        <v>292.5</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,16 +5905,16 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>29.21764377669582</v>
+        <v>26.04673424715126</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>25.60077328019116</v>
+        <v>23.62192876525893</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.4646779849535786</v>
+        <v>0.5278550201289791</v>
       </c>
       <c r="K103" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-0.03676479220363349</v>
+        <v>-8.837363513384281</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>7689</v>
+        <v>6955</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>大鵬科CLMX</t>
+          <t>邦睿生技-創</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>200.5500365346578</v>
+        <v>170.8280531804478</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>129.5</v>
+        <v>90</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,16 +5958,16 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>17.77489799734886</v>
+        <v>46.23918147653166</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>39.00789613401232</v>
+        <v>8.564715242079146</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>2.75500365346578</v>
+        <v>1.282805318044778</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>-1.236004990643405</v>
+        <v>0.03683252613306909</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>7803</v>
+        <v>6862</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>雲象科技-創</t>
+          <t>三集瑞-KY</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>193.2642916771634</v>
+        <v>164.6415993592005</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>14.05</v>
+        <v>133</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>21.42492594655155</v>
+        <v>42.88363010583378</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>27.42058379178776</v>
+        <v>15.71230674426657</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>1.226429167716345</v>
+        <v>0.4773898141417786</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-0.2929836700446683</v>
+        <v>-1.115071958290637</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>6994</v>
+        <v>6863</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>富威電力</t>
+          <t>永道-KY</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>187.6365819522924</v>
+        <v>163.103764062786</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>24.8</v>
+        <v>95</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,13 +6064,13 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>35.55468177108385</v>
+        <v>40.03632443609666</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>26.24491448712336</v>
+        <v>17.99811734155486</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.3803880216588281</v>
+        <v>0.4265669980208708</v>
       </c>
       <c r="K106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-0.1267354020755125</v>
+        <v>-0.1251140876311405</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>6922</v>
+        <v>7839</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>宸曜</t>
+          <t>達人網</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>186.9264768993949</v>
+        <v>162.4861976893032</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>194.5</v>
+        <v>43</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,13 +6117,13 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>45.76150218074234</v>
+        <v>40.2813369956158</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>17.33952796291963</v>
+        <v>26.92297046420287</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.2786182649751484</v>
+        <v>0.5297056179519567</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-1.146506082329345</v>
+        <v>-0.07208306671201881</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>7823</v>
+        <v>6903</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>奧義賽博-KY創</t>
+          <t>巨漢</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>186.1860901820725</v>
+        <v>159.1730641776667</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>74.5</v>
+        <v>299</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,13 +6170,13 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>32.24991390587944</v>
+        <v>41.44320705334401</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>31.5903707882355</v>
+        <v>19.50638009654795</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.6576625482020113</v>
+        <v>0.5000207673776802</v>
       </c>
       <c r="K108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-0.2055094763703411</v>
+        <v>-3.299622534683234</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>6951</v>
+        <v>7734</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>青新-創</t>
+          <t>印能科技</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>181.912100691137</v>
+        <v>158.2313890944335</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>67.5</v>
+        <v>2235</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,16 +6223,16 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>31.01316618992942</v>
+        <v>36.95745561580136</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>41.19507021748269</v>
+        <v>18.61494743925118</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.6294196549781778</v>
+        <v>0.545756833530492</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>0.02304230042224198</v>
+        <v>-29.92112222099807</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>6921</v>
+        <v>6923</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>嘉雨思-創</t>
+          <t>中台</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>180.1348848325586</v>
+        <v>155.1312076902498</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>65.5</v>
+        <v>71.5</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>53.07549042563109</v>
+        <v>31.15340678292196</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>14.80872838701056</v>
+        <v>10.79851077314652</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.09372532387957233</v>
+        <v>0.3792444600082324</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>-0.7138303327008231</v>
+        <v>-0.1205463483166138</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>6869</v>
+        <v>6969</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>雲豹能源</t>
+          <t>成信實業*-創</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>176.9793262145451</v>
+        <v>154.5243155495477</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>67.3</v>
+        <v>28.05</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>44.76671033694203</v>
+        <v>36.58153114512177</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>17.17918502280378</v>
+        <v>14.10798663650725</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.4395255278669921</v>
+        <v>0.4828991919861195</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>-0.5168553822966563</v>
+        <v>-0.06146829216386784</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>7768</v>
+        <v>7705</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>頌勝科技</t>
+          <t>三商餐飲</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>162.7986251556264</v>
+        <v>151.8314650014326</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>251</v>
+        <v>29.35</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,13 +6382,13 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>32.79451908846056</v>
+        <v>41.88785899671264</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>18.62200228097461</v>
+        <v>18.61126210363066</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.3649531146693966</v>
+        <v>0.170606250745183</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>-4.761721361774284</v>
+        <v>-0.004622364225198794</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>6908</v>
+        <v>7715</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>宏碁遊戲-創</t>
+          <t>裕山</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>161.7041791257712</v>
+        <v>141.9905539996136</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>24.45</v>
+        <v>25.1</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,13 +6435,13 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>20.57580081196865</v>
+        <v>29.21764400235446</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>18.23782413563235</v>
+        <v>25.60077328394916</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.6529864548855372</v>
+        <v>0.4646779849535786</v>
       </c>
       <c r="K113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>0.03096334923406174</v>
+        <v>-0.03676479214756867</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>7780</v>
+        <v>6994</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>大研生醫*</t>
+          <t>富威電力</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>161.4384634813838</v>
+        <v>127.6365819522924</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>15.45</v>
+        <v>24.8</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,13 +6488,13 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>33.27397132685032</v>
+        <v>35.55468188276215</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>17.47791131247804</v>
+        <v>26.24491452316986</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.5103585753440525</v>
+        <v>0.3803880216588281</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>-0.04501778987220656</v>
+        <v>-0.1267354020194453</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>6899</v>
+        <v>7823</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>創為精密</t>
+          <t>奧義賽博-KY創</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>160.3562013887399</v>
+        <v>126.1860901820724</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>48.5</v>
+        <v>74.5</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,13 +6541,13 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>40.78277252092214</v>
+        <v>32.24991390587944</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>21.48842750174778</v>
+        <v>31.5903707882355</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>1.466376077121713</v>
+        <v>0.6576625482020113</v>
       </c>
       <c r="K115" s="2" t="n">
         <v>1</v>
@@ -6559,31 +6559,31 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>-0.02727199969100491</v>
+        <v>-0.2055094763703411</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>6967</v>
+        <v>6951</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>汎瑋材料</t>
+          <t>青新-創</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>156.2737936783797</v>
+        <v>121.912100691137</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>67.3</v>
+        <v>67.5</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,13 +6594,13 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>41.67219795851538</v>
+        <v>31.01316633889628</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>15.49009856449944</v>
+        <v>41.19507022146991</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.6362500269332702</v>
+        <v>0.6294196549781778</v>
       </c>
       <c r="K116" s="2" t="n">
         <v>0</v>
@@ -6612,31 +6612,31 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>-0.3097279192148716</v>
+        <v>0.02304230033815147</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>7740</v>
+        <v>7722</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>熙特爾-創</t>
+          <t>LINEPAY</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>150.8732176301476</v>
+        <v>110.7071771441335</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>102</v>
+        <v>244</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,16 +6647,16 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>39.40739223794145</v>
+        <v>30.01637599921997</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>15.28106369354985</v>
+        <v>19.46075943162296</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>0.4559140112834991</v>
+        <v>0.3968459061733913</v>
       </c>
       <c r="K117" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L117" s="2" t="n">
         <v>0</v>
@@ -6665,31 +6665,31 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>0.7639385864131043</v>
+        <v>-1.026710592267595</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>7722</v>
+        <v>7768</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>LINEPAY</t>
+          <t>頌勝科技</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>150.7071771441337</v>
+        <v>102.7986251556264</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,13 +6700,13 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>30.01637617952125</v>
+        <v>32.79451908075373</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>19.46075944277282</v>
+        <v>18.62200224426735</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>0.3968459061733913</v>
+        <v>0.3649531146693966</v>
       </c>
       <c r="K118" s="2" t="n">
         <v>0</v>
@@ -6718,31 +6718,31 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>-1.026710592828305</v>
+        <v>-4.761721361774284</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>6931</v>
+        <v>6908</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>青松健康</t>
+          <t>宏碁遊戲-創</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>145.7361437513161</v>
+        <v>101.7041791257713</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>37.5</v>
+        <v>24.45</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -6753,13 +6753,13 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>32.95435803278802</v>
+        <v>20.57580060109973</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>13.60208796284546</v>
+        <v>18.23782409983614</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.975460795551073</v>
+        <v>0.6529864548855372</v>
       </c>
       <c r="K119" s="2" t="n">
         <v>0</v>
@@ -6771,31 +6771,31 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>-0.002195292232268442</v>
+        <v>0.03096334920602639</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>7728</v>
+        <v>7780</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>光焱科技</t>
+          <t>大研生醫*</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>144.3039659404951</v>
+        <v>101.4384634813834</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>531</v>
+        <v>15.45</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -6806,16 +6806,16 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>31.6223044928194</v>
+        <v>33.27398783030398</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>17.0916691046562</v>
+        <v>17.47791469458575</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.2248494483352819</v>
+        <v>0.5103585753440525</v>
       </c>
       <c r="K120" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L120" s="2" t="n">
         <v>0</v>
@@ -6824,31 +6824,31 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>-8.071995787430797</v>
+        <v>-0.04501779120680233</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>7721</v>
+        <v>6899</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>微程式</t>
+          <t>創為精密</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>140.7637333061333</v>
+        <v>100.3562013887399</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>58.4</v>
+        <v>48.5</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -6859,16 +6859,16 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>36.12529418547174</v>
+        <v>40.78277252092214</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>19.79410250061273</v>
+        <v>21.4884275993108</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>0.4350136963898769</v>
+        <v>1.466376077121713</v>
       </c>
       <c r="K121" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L121" s="2" t="n">
         <v>0</v>
@@ -6877,11 +6877,11 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>-0.2864276229746133</v>
+        <v>-0.02727199971904137</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
@@ -6898,7 +6898,7 @@
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>139.6231565428276</v>
+        <v>99.62315654282762</v>
       </c>
       <c r="E122" s="2" t="n">
         <v>89.5</v>
@@ -6912,16 +6912,16 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>44.37303194752329</v>
+        <v>44.37303184565429</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>11.77955159622661</v>
+        <v>11.77955161766125</v>
       </c>
       <c r="J122" s="2" t="n">
         <v>0.6149964743717735</v>
       </c>
       <c r="K122" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L122" s="2" t="n">
         <v>0</v>
@@ -6930,31 +6930,31 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>-0.1843392387742647</v>
+        <v>-0.1843392383537484</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>7820</v>
+        <v>6967</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>立盈</t>
+          <t>汎瑋材料</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>137.5374752761108</v>
+        <v>96.27379367837966</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>104</v>
+        <v>67.3</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -6965,13 +6965,13 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>51.98524092591327</v>
+        <v>41.67219802824427</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>11.41321184485891</v>
+        <v>15.49009862349207</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>0.1268444531594686</v>
+        <v>0.6362500269332702</v>
       </c>
       <c r="K123" s="2" t="n">
         <v>0</v>
@@ -6983,31 +6983,31 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>-0.1344494814490549</v>
+        <v>-0.3097279192148716</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, williams_r_recovery, above_ichimoku_cloud</t>
+          <t>avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>7753</v>
+        <v>7740</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>星亞</t>
+          <t>熙特爾-創</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
         <v/>
       </c>
       <c r="D124" s="2" t="n">
-        <v>133.0944017801717</v>
+        <v>90.87321763014756</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>35</v>
+        <v>102</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -7018,13 +7018,13 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>41.47623350262342</v>
+        <v>39.40739183303705</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>14.30932353196494</v>
+        <v>15.28106370856302</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>0.1128713191498537</v>
+        <v>0.4559140112834991</v>
       </c>
       <c r="K124" s="2" t="n">
         <v>0</v>
@@ -7036,31 +7036,31 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>-0.03148508065868605</v>
+        <v>0.7639385876746161</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>7732</v>
+        <v>7728</v>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>金興精密</t>
+          <t>光焱科技</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
         <v/>
       </c>
       <c r="D125" s="2" t="n">
-        <v>131.2893259748581</v>
+        <v>84.30396594049499</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>0</v>
+        <v>531</v>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
@@ -7071,13 +7071,13 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>23.88543518001083</v>
+        <v>31.6223043855741</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>8.153758174578577</v>
+        <v>17.09166911162493</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>0.02013403514827279</v>
+        <v>0.2248494483352819</v>
       </c>
       <c r="K125" s="2" t="n">
         <v>0</v>
@@ -7089,31 +7089,31 @@
         <v>-1</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>-2.110025412904553</v>
+        <v>-8.071995784066832</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>6906</v>
+        <v>7721</v>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>現觀科</t>
+          <t>微程式</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
         <v/>
       </c>
       <c r="D126" s="2" t="n">
-        <v>129.4518332609744</v>
+        <v>80.763733306124</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>75.7</v>
+        <v>58.4</v>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
@@ -7124,13 +7124,13 @@
         <v>0</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>35.95912592283922</v>
+        <v>36.12529428757868</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>19.24489215050487</v>
+        <v>19.79410252846607</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>0.9167521946204261</v>
+        <v>0.4350136963898769</v>
       </c>
       <c r="K126" s="2" t="n">
         <v>0</v>
@@ -7142,31 +7142,31 @@
         <v>-1</v>
       </c>
       <c r="N126" s="2" t="n">
-        <v>-0.5334500721629366</v>
+        <v>-0.286427623311018</v>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
-        <v>6969</v>
+        <v>7753</v>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>成信實業*-創</t>
+          <t>星亞</t>
         </is>
       </c>
       <c r="C127" s="2" t="n">
         <v/>
       </c>
       <c r="D127" s="2" t="n">
-        <v>99.52431554954777</v>
+        <v>73.09440178017165</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>28.05</v>
+        <v>35</v>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
@@ -7177,13 +7177,13 @@
         <v>0</v>
       </c>
       <c r="H127" s="2" t="n">
-        <v>36.58153112471796</v>
+        <v>41.47623333430697</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>14.10798664852033</v>
+        <v>14.30932351808797</v>
       </c>
       <c r="J127" s="2" t="n">
-        <v>0.4828991919861195</v>
+        <v>0.1128713191498537</v>
       </c>
       <c r="K127" s="2" t="n">
         <v>0</v>
@@ -7195,31 +7195,31 @@
         <v>-1</v>
       </c>
       <c r="N127" s="2" t="n">
-        <v>-0.06146829205173154</v>
+        <v>-0.03148508057458682</v>
       </c>
       <c r="O127" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
-        <v>7705</v>
+        <v>7732</v>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>三商餐飲</t>
+          <t>金興精密</t>
         </is>
       </c>
       <c r="C128" s="2" t="n">
         <v/>
       </c>
       <c r="D128" s="2" t="n">
-        <v>96.83146500143243</v>
+        <v>71.28932597485823</v>
       </c>
       <c r="E128" s="2" t="n">
-        <v>29.35</v>
+        <v>0</v>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
@@ -7230,13 +7230,13 @@
         <v>0</v>
       </c>
       <c r="H128" s="2" t="n">
-        <v>41.88785885061007</v>
+        <v>23.88543517281462</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>18.61126206719989</v>
+        <v>8.15375818212153</v>
       </c>
       <c r="J128" s="2" t="n">
-        <v>0.170606250745183</v>
+        <v>0.02013403514827279</v>
       </c>
       <c r="K128" s="2" t="n">
         <v>0</v>
@@ -7248,11 +7248,11 @@
         <v>-1</v>
       </c>
       <c r="N128" s="2" t="n">
-        <v>-0.00462236414109729</v>
+        <v>-2.110025412820456</v>
       </c>
       <c r="O128" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>avoid_chase</t>
         </is>
       </c>
     </row>
